--- a/docs/due-diligence/syntx/models/dev-cost-estimate.xlsx
+++ b/docs/due-diligence/syntx/models/dev-cost-estimate.xlsx
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x — параллельные AI-агенты, без издержек человеческой синхронизации</t>
         </is>
       </c>
     </row>
@@ -561,11 +561,11 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x — издержки координации между людьми перевешивают выигрыш от 2-й пары рук</t>
         </is>
       </c>
     </row>
